--- a/连板前瞻验证数据库.xlsx
+++ b/连板前瞻验证数据库.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方向命中率" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则验证" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="竞价信号" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="行情快照" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="连板梯队" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -517,27 +519,32 @@
           <t>板块</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>今日结果</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>收盘涨跌幅%</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>可执行收益%</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>断板亏损%</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>归因/备注</t>
         </is>
@@ -582,19 +589,24 @@
           <t>电子胶+羊概念</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>高标</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="K2" s="2" t="n">
         <v>-4.77</v>
       </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n">
         <v>-4.77</v>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>纯玄学高标退潮</t>
         </is>
@@ -639,19 +651,24 @@
           <t>医疗+羊概念</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>高标</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>✗ 跌停</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="2" t="n">
         <v>-10.02</v>
       </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n">
         <v>-10.02</v>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>换手26.86%分歧过度直接跌停</t>
         </is>
@@ -696,17 +713,22 @@
           <t>装修</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>高标</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="K4" s="2" t="n">
         <v>7.73</v>
       </c>
-      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>巨量换手未封住,装修无协同</t>
         </is>
@@ -751,19 +773,24 @@
           <t>CPO</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="K5" s="2" t="n">
         <v>-1.6</v>
       </c>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n">
         <v>-1.6</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>CPO高潮后期资金兑现(板块净流出228亿)</t>
         </is>
@@ -808,19 +835,24 @@
           <t>ABF覆铜板</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>半导体高位出清</t>
         </is>
@@ -865,17 +897,22 @@
           <t>CPO</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="K7" s="2" t="n">
         <v>0.36</v>
       </c>
-      <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>CPO板块集体退潮</t>
         </is>
@@ -920,19 +957,24 @@
           <t>中药</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级4板</t>
         </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>医药发酵期(非高潮)独立晋级</t>
         </is>
@@ -977,19 +1019,24 @@
           <t>CPO</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级3板</t>
         </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>秒板转弱转强,换手适中,CPO内部分化存活</t>
         </is>
@@ -1034,19 +1081,24 @@
           <t>创新药</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="K10" s="2" t="n">
         <v>-5.78</v>
       </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n">
         <v>-5.78</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>创新药无独立催化,依赖神奇带队跟风乏力</t>
         </is>
@@ -1091,19 +1143,24 @@
           <t>CPO散热</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级3板20cm</t>
         </is>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>20</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>中际旭创入股产业催化,独立于板块退潮</t>
         </is>
@@ -1148,19 +1205,24 @@
           <t>机器人</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级3板</t>
         </is>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>秒板惜售+宇树上市预期支撑</t>
         </is>
@@ -1203,17 +1265,22 @@
           <t>先进封装</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>✗ 未晋级</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="K13" s="2" t="n">
         <v>2.02</v>
       </c>
-      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>封单22.7亿难敌板块退潮</t>
         </is>
@@ -1256,17 +1323,22 @@
           <t>CPO</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>CPO</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>✗ 未晋级</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="K14" s="2" t="n">
         <v>2.82</v>
       </c>
-      <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>CPO板块溃退,业绩好难敌情绪</t>
         </is>
@@ -1309,19 +1381,24 @@
           <t>农业</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>农业</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级2板</t>
         </is>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>农业低位新主线,粮食安全+天气催化</t>
         </is>
@@ -1366,19 +1443,24 @@
           <t>汽车零部/机器人</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>机器人</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>✗ 跌停</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="K16" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>系统性退潮日高位无差别杀跌,宇树高开抽血</t>
         </is>
@@ -1423,19 +1505,24 @@
           <t>休闲食品</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>消费/食品</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>✗ 跌停</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="K17" s="2" t="n">
         <v>-10.02</v>
       </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n">
         <v>-10.02</v>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>消费独苗无板块协同,一鸣跌停拖累食品链</t>
         </is>
@@ -1480,19 +1567,24 @@
           <t>化学制药</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级5板</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="K18" s="2" t="n">
         <v>10.05</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>市场唯一高度板,退潮日卡位最高标(高开5.54%超区间被规则漏杀)</t>
         </is>
@@ -1537,17 +1629,22 @@
           <t>化学制药</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>医药</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>✗ 未晋级</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="K19" s="2" t="n">
         <v>7.49</v>
       </c>
-      <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>医药1进2炸板,跟风神奇但承接不足</t>
         </is>
@@ -1592,17 +1689,22 @@
           <t>养殖业</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>农业</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="K20" s="2" t="n">
         <v>11.8</v>
       </c>
-      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>创业板20cm3板高度难破,高开13.35%兑现盘集中</t>
         </is>
@@ -1647,19 +1749,24 @@
           <t>农化</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>农业</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级3板</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>10.02</v>
       </c>
-      <c r="K21" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>农业化肥核心龙,逆势主线资金抱团</t>
         </is>
@@ -1704,19 +1811,24 @@
           <t>农产品加工</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>农业</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级3板一字</t>
         </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>9.99</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>9.99</v>
       </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>农业先锋龙头,一字加速</t>
         </is>
@@ -1761,17 +1873,22 @@
           <t>服装家纺</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>消费/食品</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="K23" s="2" t="n">
         <v>5.04</v>
       </c>
-      <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>极致惜售但板块无协同+高开7.69%超区间兑现</t>
         </is>
@@ -1816,19 +1933,24 @@
           <t>农产品加工</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>农业</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>✓ 晋级3板</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="K24" s="2" t="n">
         <v>10.01</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>7.9</v>
       </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>农业补涨,板块梯队共振(高开+2.06%竞价可买入+7.9%)</t>
         </is>
@@ -1873,17 +1995,22 @@
           <t>光学光电</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>光学光电</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>✗ 断板</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="K25" s="2" t="n">
         <v>3.2</v>
       </c>
-      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>妖股高位退潮日资金离场反抽乏力</t>
         </is>
@@ -3226,4 +3353,1372 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>涨停家数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>跌停家数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>炸板家数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>炸板率%</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>连板家数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>昨日连板</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>晋级率%</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最高标板数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>情绪温度</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>分区</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>总开关判定</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>高标跌停</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>正常≤5成</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>涨停79跌停5炸板23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>空仓观望(退潮确认)</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>涨停29跌停14炸板9</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>连板数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>板块</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>换手率%</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>封板时间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>炸板次数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>流通市值(亿)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>600613</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>神奇制药</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>化学制药</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>92502</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>603089</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>正裕工业</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>汽车零部</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>92500</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>300684</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>中石科技</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>电子化学</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>93312</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>198.4</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>600353</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>旭光电子</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>其他电子</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>93305</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>311.1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>002820</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>桂发祥</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>休闲食品</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>92500</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>605179</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>一鸣食品</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>饮料乳品</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>145659</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>603580</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>艾艾精工</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>塑料</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>93535</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>603221</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>爱丽家居</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>家居用品</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>94449</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>000505</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>京粮控股</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>农产品加</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>101933</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>001229</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>魅视科技</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>计算机设</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>93109</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>603936</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>博敏电子</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>元件</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>93104</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>603958</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>哈森股份</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>服装家纺</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>92501</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>603823</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>百合花</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>化学制品</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>93552</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>300313</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>天山生物</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>养殖业</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>93130</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>600313</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>农发种业</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>93808</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>603395</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>红四方</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>农化制品</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>93011</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>000735</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>罗 牛 山</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>养殖业</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>94521</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>600127</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>农产品加</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>93057</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>600613</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>神奇制药</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>化学制药</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>93044</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>603395</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>红四方</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>农化制品</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>92502</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>000505</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>京粮控股</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>农产品加</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>93133</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>600313</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>农发种业</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>种植业</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>92501</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>600127</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>农产品加</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>92502</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>000020</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>深华发Ａ</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>光学光电</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>93000</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>000526</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>学大教育</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>93324</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>002953</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>日丰股份</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>电网设备</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>92500</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>连板</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/连板前瞻验证数据库.xlsx
+++ b/连板前瞻验证数据库.xlsx
@@ -3491,7 +3491,7 @@
           <t>正常≤5成</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>涨停79跌停5炸板23</t>
@@ -3505,35 +3505,35 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>18</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>44.4</v>
+        <v>38.9</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>冰点</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3541,10 +3541,10 @@
           <t>空仓观望(退潮确认)</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>涨停29跌停14炸板9</t>
+          <t>涨停36跌停114炸板12</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4390,33 +4390,33 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>600613</t>
+          <t>603395</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>神奇制药</t>
+          <t>红四方</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>化学制药</t>
+          <t>农化制品</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.77</v>
+        <v>18.11</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>93044</v>
+        <v>92502</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>40.9</v>
+        <v>18.9</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -4432,12 +4432,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>603395</t>
+          <t>600127</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>红四方</t>
+          <t>金健米业</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -4445,20 +4445,20 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>农化制品</t>
+          <t>农产品加</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>16.6</v>
+        <v>4.56</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>92502</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.9</v>
+        <v>50.2</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6.97</v>
+        <v>10.74</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>93133</v>
@@ -4516,16 +4516,16 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>600313</t>
+          <t>600371</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>农发种业</t>
+          <t>万向德农</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -4533,16 +4533,16 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2.63</v>
+        <v>18.17</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>92501</v>
+        <v>93118</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>80.7</v>
+        <v>26.2</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -4558,33 +4558,33 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>600127</t>
+          <t>000020</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>金健米业</t>
+          <t>深华发Ａ</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>农产品加</t>
+          <t>光学光电</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>2.78</v>
+        <v>10.57</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>92502</v>
+        <v>93000</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>50.2</v>
+        <v>24.9</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>000020</t>
+          <t>000526</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>深华发Ａ</t>
+          <t>学大教育</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
@@ -4613,20 +4613,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>光学光电</t>
+          <t>教育</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>9.66</v>
+        <v>7.7</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>93000</v>
+        <v>93324</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.9</v>
+        <v>47.5</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>000526</t>
+          <t>002953</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>学大教育</t>
+          <t>日丰股份</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
@@ -4655,64 +4655,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>教育</t>
+          <t>电网设备</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>6.86</v>
+        <v>8.33</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>93324</v>
+        <v>92500</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>47.5</v>
+        <v>33</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>连板</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>002953</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>日丰股份</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>电网设备</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>92500</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>连板</t>
         </is>
